--- a/data/input/Carreras/Maestro materias.xlsx
+++ b/data/input/Carreras/Maestro materias.xlsx
@@ -4040,7 +4040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="1">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="1">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="1">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="1">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="1">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="1">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="1">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="1">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="1">
       <c r="A16" s="1" t="s">
         <v>35</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="1">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="1">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="1">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="1">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="1">
       <c r="A24" s="1" t="s">
         <v>52</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="1">
       <c r="A26" s="1" t="s">
         <v>56</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="1">
       <c r="A27" s="1" t="s">
         <v>58</v>
       </c>
@@ -4560,7 +4560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="1">
       <c r="A28" s="1" t="s">
         <v>60</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="1">
       <c r="A29" s="1" t="s">
         <v>62</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="1">
       <c r="A30" s="1" t="s">
         <v>64</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1">
       <c r="A31" s="1" t="s">
         <v>66</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="1">
       <c r="A32" s="1" t="s">
         <v>68</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="1">
       <c r="A33" s="1" t="s">
         <v>70</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="1">
       <c r="A34" s="1" t="s">
         <v>72</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="1">
       <c r="A35" s="1" t="s">
         <v>74</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1">
       <c r="A36" s="1" t="s">
         <v>76</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1">
       <c r="A37" s="1" t="s">
         <v>77</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="1">
       <c r="A38" s="1" t="s">
         <v>79</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="1">
       <c r="A39" s="1" t="s">
         <v>81</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="1">
       <c r="A40" s="1" t="s">
         <v>83</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="1">
       <c r="A41" s="1" t="s">
         <v>85</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="1">
       <c r="A42" s="1" t="s">
         <v>86</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="1">
       <c r="A43" s="1" t="s">
         <v>88</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="1">
       <c r="A44" s="1" t="s">
         <v>90</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="1">
       <c r="A45" s="1" t="s">
         <v>92</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="1">
       <c r="A46" s="1" t="s">
         <v>94</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="1">
       <c r="A47" s="1" t="s">
         <v>96</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="1">
       <c r="A48" s="1" t="s">
         <v>98</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="1">
       <c r="A49" s="1" t="s">
         <v>100</v>
       </c>
@@ -5000,7 +5000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="1">
       <c r="A50" s="1" t="s">
         <v>102</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="1">
       <c r="A51" s="1" t="s">
         <v>103</v>
       </c>
@@ -5040,7 +5040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="1">
       <c r="A52" s="1" t="s">
         <v>105</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="1">
       <c r="A53" s="1" t="s">
         <v>107</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="1">
       <c r="A54" s="1" t="s">
         <v>109</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="1">
       <c r="A55" s="1" t="s">
         <v>111</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1">
       <c r="A56" s="1" t="s">
         <v>113</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="1">
       <c r="A57" s="1" t="s">
         <v>115</v>
       </c>
@@ -5160,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="1">
       <c r="A58" s="1" t="s">
         <v>117</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="1">
       <c r="A59" s="1" t="s">
         <v>119</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="1">
       <c r="A60" s="1" t="s">
         <v>122</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="1">
       <c r="A61" s="1" t="s">
         <v>124</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="1">
       <c r="A62" s="1" t="s">
         <v>126</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="1">
       <c r="A63" s="1" t="s">
         <v>128</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="1">
       <c r="A64" s="1" t="s">
         <v>130</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="1">
       <c r="A65" s="1" t="s">
         <v>132</v>
       </c>
@@ -5320,7 +5320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="1">
       <c r="A66" s="1" t="s">
         <v>134</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="1">
       <c r="A67" s="1" t="s">
         <v>136</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="1">
       <c r="A68" s="1" t="s">
         <v>138</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="1">
       <c r="A69" s="1" t="s">
         <v>140</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="1">
       <c r="A70" s="1" t="s">
         <v>142</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="1">
       <c r="A71" s="1" t="s">
         <v>144</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72" s="1" t="s">
         <v>146</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="1">
       <c r="A73" s="1" t="s">
         <v>148</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="1">
       <c r="A74" s="1" t="s">
         <v>150</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="1">
       <c r="A75" s="1" t="s">
         <v>152</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="1">
       <c r="A76" s="1" t="s">
         <v>154</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="1">
       <c r="A77" s="1" t="s">
         <v>156</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="1">
       <c r="A78" s="1" t="s">
         <v>158</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="1">
       <c r="A79" s="1" t="s">
         <v>160</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="1">
       <c r="A80" s="1" t="s">
         <v>162</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="1">
       <c r="A81" s="1" t="s">
         <v>164</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="1">
       <c r="A82" s="1" t="s">
         <v>166</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="1">
       <c r="A83" s="1" t="s">
         <v>168</v>
       </c>
@@ -5680,7 +5680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="1">
       <c r="A84" s="1" t="s">
         <v>170</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="1">
       <c r="A85" s="1" t="s">
         <v>172</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="1">
       <c r="A86" s="1" t="s">
         <v>173</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="1">
       <c r="A87" s="1" t="s">
         <v>175</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="1">
       <c r="A88" s="1" t="s">
         <v>177</v>
       </c>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="1">
       <c r="A89" s="1" t="s">
         <v>179</v>
       </c>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="1">
       <c r="A90" s="1" t="s">
         <v>181</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="1">
       <c r="A91" s="1" t="s">
         <v>183</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="1">
       <c r="A92" s="1" t="s">
         <v>185</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="1">
       <c r="A93" s="1" t="s">
         <v>187</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="1">
       <c r="A94" s="1" t="s">
         <v>189</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="1">
       <c r="A95" s="1" t="s">
         <v>191</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96" s="1" t="s">
         <v>193</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="1">
       <c r="A97" s="1" t="s">
         <v>195</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="1">
       <c r="A98" s="1" t="s">
         <v>197</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="1">
       <c r="A99" s="1" t="s">
         <v>199</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100" s="1" t="s">
         <v>201</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="1">
       <c r="A101" s="1" t="s">
         <v>203</v>
       </c>
@@ -6040,7 +6040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="1">
       <c r="A102" s="1" t="s">
         <v>205</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103" s="1" t="s">
         <v>206</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104" s="1" t="s">
         <v>207</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="1">
       <c r="A105" s="1" t="s">
         <v>209</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="1">
       <c r="A106" s="1" t="s">
         <v>211</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="1">
       <c r="A107" s="1" t="s">
         <v>213</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108" s="1" t="s">
         <v>215</v>
       </c>
@@ -6180,7 +6180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109" s="1" t="s">
         <v>217</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="1">
       <c r="A110" s="1" t="s">
         <v>219</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="1">
       <c r="A111" s="1" t="s">
         <v>221</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="1">
       <c r="A112" s="1" t="s">
         <v>223</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="1">
       <c r="A113" s="1" t="s">
         <v>225</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114" s="1" t="s">
         <v>227</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="1">
       <c r="A115" s="1" t="s">
         <v>229</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="1">
       <c r="A116" s="1" t="s">
         <v>231</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="1">
       <c r="A117" s="1" t="s">
         <v>233</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="1">
       <c r="A118" s="1" t="s">
         <v>235</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="1">
       <c r="A119" s="1" t="s">
         <v>237</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="1">
       <c r="A120" s="1" t="s">
         <v>238</v>
       </c>
@@ -6420,7 +6420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="1">
       <c r="A121" s="1" t="s">
         <v>240</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="1">
       <c r="A122" s="1" t="s">
         <v>241</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="1">
       <c r="A123" s="1" t="s">
         <v>243</v>
       </c>
@@ -6480,7 +6480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="1">
       <c r="A124" s="1" t="s">
         <v>245</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="1">
       <c r="A125" s="1" t="s">
         <v>247</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="1">
       <c r="A126" s="1" t="s">
         <v>249</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="1">
       <c r="A127" s="1" t="s">
         <v>251</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="1">
       <c r="A128" s="1" t="s">
         <v>253</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="1">
       <c r="A129" s="1" t="s">
         <v>255</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="1">
       <c r="A130" s="1" t="s">
         <v>257</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="1">
       <c r="A131" s="1" t="s">
         <v>259</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="1">
       <c r="A132" s="1" t="s">
         <v>261</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="1">
       <c r="A133" s="1" t="s">
         <v>263</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="1">
       <c r="A134" s="1" t="s">
         <v>265</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="1">
       <c r="A135" s="1" t="s">
         <v>267</v>
       </c>
@@ -6720,7 +6720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="1">
       <c r="A136" s="1" t="s">
         <v>269</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="1">
       <c r="A137" s="1" t="s">
         <v>271</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="1">
       <c r="A138" s="1" t="s">
         <v>273</v>
       </c>
@@ -6780,7 +6780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="1">
       <c r="A139" s="1" t="s">
         <v>275</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="1">
       <c r="A140" s="1" t="s">
         <v>277</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="1">
       <c r="A141" s="1" t="s">
         <v>278</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" hidden="1">
       <c r="A142" s="1" t="s">
         <v>279</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="1">
       <c r="A143" s="1" t="s">
         <v>281</v>
       </c>
@@ -6880,7 +6880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="1">
       <c r="A144" s="1" t="s">
         <v>283</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="1">
       <c r="A145" s="1" t="s">
         <v>285</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="1">
       <c r="A146" s="1" t="s">
         <v>287</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="1">
       <c r="A147" s="1" t="s">
         <v>289</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="1">
       <c r="A148" s="1" t="s">
         <v>291</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="1">
       <c r="A149" s="1" t="s">
         <v>293</v>
       </c>
@@ -7000,7 +7000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="1">
       <c r="A150" s="1" t="s">
         <v>295</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="1">
       <c r="A151" s="1" t="s">
         <v>297</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="1">
       <c r="A152" s="1" t="s">
         <v>299</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="1">
       <c r="A153" s="1" t="s">
         <v>301</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="1">
       <c r="A154" s="1" t="s">
         <v>303</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="1">
       <c r="A155" s="1" t="s">
         <v>305</v>
       </c>
@@ -7120,7 +7120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="1">
       <c r="A156" s="1" t="s">
         <v>307</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="1">
       <c r="A157" s="1" t="s">
         <v>309</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="1">
       <c r="A158" s="1" t="s">
         <v>311</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="1">
       <c r="A159" s="1" t="s">
         <v>313</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="1">
       <c r="A160" s="1" t="s">
         <v>315</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="1">
       <c r="A161" s="1" t="s">
         <v>316</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="1">
       <c r="A162" s="1" t="s">
         <v>318</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="1">
       <c r="A163" s="1" t="s">
         <v>320</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="1">
       <c r="A164" s="1" t="s">
         <v>322</v>
       </c>
@@ -7300,7 +7300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="1">
       <c r="A165" s="1" t="s">
         <v>324</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="1">
       <c r="A166" s="1" t="s">
         <v>326</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="1">
       <c r="A167" s="1" t="s">
         <v>328</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="1">
       <c r="A168" s="1" t="s">
         <v>330</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="1">
       <c r="A169" s="1" t="s">
         <v>332</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="1">
       <c r="A170" s="1" t="s">
         <v>334</v>
       </c>
@@ -7420,7 +7420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="1">
       <c r="A171" s="1" t="s">
         <v>335</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="1">
       <c r="A172" s="1" t="s">
         <v>337</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="1">
       <c r="A173" s="1" t="s">
         <v>339</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="1">
       <c r="A174" s="1" t="s">
         <v>341</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="1">
       <c r="A175" s="1" t="s">
         <v>343</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="1">
       <c r="A176" s="1" t="s">
         <v>345</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="1">
       <c r="A177" s="1" t="s">
         <v>347</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="1">
       <c r="A178" s="1" t="s">
         <v>349</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="1">
       <c r="A179" s="1" t="s">
         <v>351</v>
       </c>
@@ -7600,7 +7600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="1">
       <c r="A180" s="1" t="s">
         <v>353</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="1">
       <c r="A181" s="1" t="s">
         <v>355</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="1">
       <c r="A182" s="1" t="s">
         <v>356</v>
       </c>
@@ -7658,7 +7658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="1">
       <c r="A183" s="1" t="s">
         <v>358</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" hidden="1">
       <c r="A184" s="1" t="s">
         <v>360</v>
       </c>
@@ -7694,7 +7694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" hidden="1">
       <c r="A185" s="1" t="s">
         <v>362</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="1">
       <c r="A186" s="1" t="s">
         <v>364</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" hidden="1">
       <c r="A187" s="1" t="s">
         <v>365</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" hidden="1">
       <c r="A188" s="1" t="s">
         <v>367</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" hidden="1">
       <c r="A189" s="1" t="s">
         <v>368</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="1">
       <c r="A190" s="1" t="s">
         <v>370</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" hidden="1">
       <c r="A191" s="1" t="s">
         <v>372</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" hidden="1">
       <c r="A192" s="1" t="s">
         <v>374</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" hidden="1">
       <c r="A193" s="1" t="s">
         <v>376</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" hidden="1">
       <c r="A194" s="1" t="s">
         <v>378</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" hidden="1">
       <c r="A195" s="1" t="s">
         <v>379</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" hidden="1">
       <c r="A196" s="1" t="s">
         <v>381</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="1">
       <c r="A197" s="1" t="s">
         <v>383</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" hidden="1">
       <c r="A198" s="1" t="s">
         <v>385</v>
       </c>
@@ -7974,7 +7974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" hidden="1">
       <c r="A199" s="1" t="s">
         <v>387</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" hidden="1">
       <c r="A200" s="1" t="s">
         <v>389</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" hidden="1">
       <c r="A201" s="1" t="s">
         <v>391</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" hidden="1">
       <c r="A202" s="1" t="s">
         <v>393</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="1">
       <c r="A203" s="1" t="s">
         <v>395</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="1">
       <c r="A204" s="1" t="s">
         <v>397</v>
       </c>
@@ -8094,7 +8094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" hidden="1">
       <c r="A205" s="1" t="s">
         <v>399</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" hidden="1">
       <c r="A206" s="1" t="s">
         <v>401</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" hidden="1">
       <c r="A207" s="1" t="s">
         <v>403</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" hidden="1">
       <c r="A208" s="1" t="s">
         <v>405</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" hidden="1">
       <c r="A209" s="1" t="s">
         <v>407</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" hidden="1">
       <c r="A210" s="1" t="s">
         <v>409</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" hidden="1">
       <c r="A211" s="1" t="s">
         <v>411</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" hidden="1">
       <c r="A212" s="1" t="s">
         <v>413</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" hidden="1">
       <c r="A213" s="1" t="s">
         <v>415</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" hidden="1">
       <c r="A214" s="1" t="s">
         <v>417</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" hidden="1">
       <c r="A215" s="1" t="s">
         <v>419</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" hidden="1">
       <c r="A216" s="1" t="s">
         <v>421</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" hidden="1">
       <c r="A217" s="1" t="s">
         <v>423</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" hidden="1">
       <c r="A218" s="1" t="s">
         <v>425</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" hidden="1">
       <c r="A219" s="1" t="s">
         <v>427</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" hidden="1">
       <c r="A220" s="1" t="s">
         <v>429</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" hidden="1">
       <c r="A221" s="1" t="s">
         <v>431</v>
       </c>
@@ -8434,7 +8434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" hidden="1">
       <c r="A222" s="1" t="s">
         <v>433</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="1">
       <c r="A223" s="1" t="s">
         <v>435</v>
       </c>
@@ -8474,7 +8474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" hidden="1">
       <c r="A224" s="1" t="s">
         <v>437</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" hidden="1">
       <c r="A225" s="1" t="s">
         <v>439</v>
       </c>
@@ -8514,7 +8514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" hidden="1">
       <c r="A226" s="1" t="s">
         <v>441</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" hidden="1">
       <c r="A227" s="1" t="s">
         <v>443</v>
       </c>
@@ -8554,7 +8554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" hidden="1">
       <c r="A228" s="1" t="s">
         <v>445</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" hidden="1">
       <c r="A229" s="1" t="s">
         <v>447</v>
       </c>
@@ -8594,7 +8594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" hidden="1">
       <c r="A230" s="1" t="s">
         <v>449</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" hidden="1">
       <c r="A231" s="1" t="s">
         <v>451</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" hidden="1">
       <c r="A232" s="1" t="s">
         <v>453</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" hidden="1">
       <c r="A233" s="1" t="s">
         <v>455</v>
       </c>
@@ -8674,7 +8674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" hidden="1">
       <c r="A234" s="1" t="s">
         <v>457</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" hidden="1">
       <c r="A235" s="1" t="s">
         <v>459</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" hidden="1">
       <c r="A236" s="1" t="s">
         <v>461</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" hidden="1">
       <c r="A237" s="1" t="s">
         <v>463</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" hidden="1">
       <c r="A238" s="1" t="s">
         <v>465</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" hidden="1">
       <c r="A239" s="1" t="s">
         <v>467</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" hidden="1">
       <c r="A240" s="1" t="s">
         <v>469</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" hidden="1">
       <c r="A241" s="1" t="s">
         <v>471</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" hidden="1">
       <c r="A242" s="1" t="s">
         <v>473</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" hidden="1">
       <c r="A243" s="1" t="s">
         <v>475</v>
       </c>
@@ -8874,7 +8874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" hidden="1">
       <c r="A244" s="1" t="s">
         <v>477</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" hidden="1">
       <c r="A245" s="1" t="s">
         <v>479</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" hidden="1">
       <c r="A246" s="1" t="s">
         <v>481</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" hidden="1">
       <c r="A247" s="1" t="s">
         <v>483</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" hidden="1">
       <c r="A248" s="1" t="s">
         <v>485</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" hidden="1">
       <c r="A249" s="1" t="s">
         <v>487</v>
       </c>
@@ -8994,7 +8994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" hidden="1">
       <c r="A250" s="1" t="s">
         <v>489</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" hidden="1">
       <c r="A251" s="1" t="s">
         <v>491</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" hidden="1">
       <c r="A252" s="1" t="s">
         <v>493</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" hidden="1">
       <c r="A253" s="1" t="s">
         <v>495</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" hidden="1">
       <c r="A254" s="1" t="s">
         <v>497</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" hidden="1">
       <c r="A255" s="1" t="s">
         <v>499</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" hidden="1">
       <c r="A256" s="1" t="s">
         <v>500</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" hidden="1">
       <c r="A257" s="1" t="s">
         <v>502</v>
       </c>
@@ -9146,7 +9146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" hidden="1">
       <c r="A258" s="1" t="s">
         <v>504</v>
       </c>
@@ -9164,7 +9164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" hidden="1">
       <c r="A259" s="1" t="s">
         <v>506</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" hidden="1">
       <c r="A260" s="1" t="s">
         <v>508</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" hidden="1">
       <c r="A261" s="1" t="s">
         <v>510</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" hidden="1">
       <c r="A262" s="1" t="s">
         <v>512</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" hidden="1">
       <c r="A263" s="1" t="s">
         <v>514</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" hidden="1">
       <c r="A264" s="1" t="s">
         <v>515</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" hidden="1">
       <c r="A265" s="1" t="s">
         <v>516</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" hidden="1">
       <c r="A266" s="1" t="s">
         <v>518</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" hidden="1">
       <c r="A267" s="1" t="s">
         <v>519</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" hidden="1">
       <c r="A268" s="1" t="s">
         <v>520</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" hidden="1">
       <c r="A269" s="1" t="s">
         <v>522</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" hidden="1">
       <c r="A270" s="1" t="s">
         <v>524</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" hidden="1">
       <c r="A271" s="1" t="s">
         <v>526</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" hidden="1">
       <c r="A272" s="1" t="s">
         <v>528</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" hidden="1">
       <c r="A273" s="1" t="s">
         <v>530</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" hidden="1">
       <c r="A274" s="1" t="s">
         <v>532</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" hidden="1">
       <c r="A275" s="1" t="s">
         <v>534</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" hidden="1">
       <c r="A276" s="1" t="s">
         <v>536</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" hidden="1">
       <c r="A283" s="1" t="s">
         <v>549</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" hidden="1">
       <c r="A284" s="1" t="s">
         <v>550</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" hidden="1">
       <c r="A285" s="1" t="s">
         <v>552</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" hidden="1">
       <c r="A286" s="1" t="s">
         <v>554</v>
       </c>
@@ -9712,7 +9712,7 @@
       <c r="C286" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D286" s="1">
+      <c r="D286" s="4">
         <v>4.0</v>
       </c>
       <c r="E286" s="1" t="s">
@@ -9722,7 +9722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" hidden="1">
       <c r="A287" s="1" t="s">
         <v>555</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" hidden="1">
       <c r="A288" s="1" t="s">
         <v>557</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" hidden="1">
       <c r="A289" s="1" t="s">
         <v>559</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" hidden="1">
       <c r="A290" s="1" t="s">
         <v>560</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" hidden="1">
       <c r="A291" s="1" t="s">
         <v>562</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" hidden="1">
       <c r="A292" s="1" t="s">
         <v>564</v>
       </c>
@@ -9842,7 +9842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" hidden="1">
       <c r="A293" s="1" t="s">
         <v>566</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" hidden="1">
       <c r="A294" s="1" t="s">
         <v>568</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" hidden="1">
       <c r="A295" s="1" t="s">
         <v>570</v>
       </c>
@@ -9902,7 +9902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" hidden="1">
       <c r="A296" s="1" t="s">
         <v>572</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" hidden="1">
       <c r="A297" s="1" t="s">
         <v>574</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" hidden="1">
       <c r="A298" s="1" t="s">
         <v>576</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" hidden="1">
       <c r="A299" s="1" t="s">
         <v>578</v>
       </c>
@@ -9982,7 +9982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" hidden="1">
       <c r="A300" s="1" t="s">
         <v>580</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" hidden="1">
       <c r="A301" s="1" t="s">
         <v>582</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" hidden="1">
       <c r="A302" s="1" t="s">
         <v>584</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" hidden="1">
       <c r="A303" s="1" t="s">
         <v>586</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" hidden="1">
       <c r="A304" s="1" t="s">
         <v>588</v>
       </c>
@@ -10082,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" hidden="1">
       <c r="A305" s="1" t="s">
         <v>590</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" hidden="1">
       <c r="A306" s="1" t="s">
         <v>592</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" hidden="1">
       <c r="A307" s="1" t="s">
         <v>594</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" hidden="1">
       <c r="A308" s="1" t="s">
         <v>596</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" hidden="1">
       <c r="A309" s="1" t="s">
         <v>598</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" hidden="1">
       <c r="A310" s="1" t="s">
         <v>600</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" hidden="1">
       <c r="A311" s="1" t="s">
         <v>602</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" hidden="1">
       <c r="A312" s="1" t="s">
         <v>604</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" hidden="1">
       <c r="A313" s="1" t="s">
         <v>606</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" hidden="1">
       <c r="A314" s="1" t="s">
         <v>608</v>
       </c>
@@ -10282,7 +10282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" hidden="1">
       <c r="A315" s="1" t="s">
         <v>610</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" hidden="1">
       <c r="A316" s="1" t="s">
         <v>612</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" hidden="1">
       <c r="A317" s="1" t="s">
         <v>614</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" hidden="1">
       <c r="A318" s="1" t="s">
         <v>616</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" hidden="1">
       <c r="A319" s="1" t="s">
         <v>618</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" hidden="1">
       <c r="A320" s="1" t="s">
         <v>620</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" hidden="1">
       <c r="A321" s="1" t="s">
         <v>622</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" hidden="1">
       <c r="A322" s="1" t="s">
         <v>624</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" hidden="1">
       <c r="A323" s="1" t="s">
         <v>626</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" hidden="1">
       <c r="A324" s="1" t="s">
         <v>627</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" hidden="1">
       <c r="A325" s="1" t="s">
         <v>629</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" hidden="1">
       <c r="A326" s="1" t="s">
         <v>631</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" hidden="1">
       <c r="A327" s="1" t="s">
         <v>633</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" hidden="1">
       <c r="A328" s="1" t="s">
         <v>635</v>
       </c>
@@ -10562,7 +10562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" hidden="1">
       <c r="A329" s="1" t="s">
         <v>636</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" hidden="1">
       <c r="A330" s="1" t="s">
         <v>638</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" hidden="1">
       <c r="A331" s="1" t="s">
         <v>640</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" hidden="1">
       <c r="A332" s="1" t="s">
         <v>642</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" hidden="1">
       <c r="A333" s="1" t="s">
         <v>644</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" hidden="1">
       <c r="A334" s="1" t="s">
         <v>646</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" hidden="1">
       <c r="A335" s="1" t="s">
         <v>648</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" hidden="1">
       <c r="A336" s="1" t="s">
         <v>650</v>
       </c>
@@ -10722,7 +10722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" hidden="1">
       <c r="A337" s="1" t="s">
         <v>652</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" hidden="1">
       <c r="A338" s="1" t="s">
         <v>654</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" hidden="1">
       <c r="A339" s="1" t="s">
         <v>656</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" hidden="1">
       <c r="A340" s="1" t="s">
         <v>657</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" hidden="1">
       <c r="A341" s="1" t="s">
         <v>659</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" hidden="1">
       <c r="A342" s="1" t="s">
         <v>661</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" hidden="1">
       <c r="A343" s="1" t="s">
         <v>663</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" hidden="1">
       <c r="A344" s="1" t="s">
         <v>665</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" hidden="1">
       <c r="A345" s="1" t="s">
         <v>667</v>
       </c>
@@ -10902,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" hidden="1">
       <c r="A346" s="1" t="s">
         <v>669</v>
       </c>
@@ -10922,7 +10922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" hidden="1">
       <c r="A347" s="1" t="s">
         <v>671</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" hidden="1">
       <c r="A348" s="1" t="s">
         <v>673</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" hidden="1">
       <c r="A349" s="1" t="s">
         <v>675</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" hidden="1">
       <c r="A350" s="1" t="s">
         <v>677</v>
       </c>
@@ -11002,7 +11002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" hidden="1">
       <c r="A351" s="1" t="s">
         <v>679</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" hidden="1">
       <c r="A352" s="1" t="s">
         <v>681</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" hidden="1">
       <c r="A353" s="1" t="s">
         <v>683</v>
       </c>
@@ -11062,7 +11062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" hidden="1">
       <c r="A354" s="1" t="s">
         <v>684</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" hidden="1">
       <c r="A355" s="1" t="s">
         <v>686</v>
       </c>
@@ -11102,7 +11102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" hidden="1">
       <c r="A356" s="1" t="s">
         <v>688</v>
       </c>
@@ -11122,7 +11122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" hidden="1">
       <c r="A357" s="1" t="s">
         <v>690</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" hidden="1">
       <c r="A358" s="1" t="s">
         <v>692</v>
       </c>
@@ -11162,7 +11162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" hidden="1">
       <c r="A359" s="1" t="s">
         <v>694</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" hidden="1">
       <c r="A360" s="1" t="s">
         <v>696</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" hidden="1">
       <c r="A361" s="1" t="s">
         <v>698</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" hidden="1">
       <c r="A362" s="1" t="s">
         <v>700</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" hidden="1">
       <c r="A363" s="1" t="s">
         <v>702</v>
       </c>
@@ -11262,7 +11262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" hidden="1">
       <c r="A364" s="1" t="s">
         <v>703</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" hidden="1">
       <c r="A365" s="1" t="s">
         <v>705</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" hidden="1">
       <c r="A366" s="1" t="s">
         <v>707</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" hidden="1">
       <c r="A367" s="1" t="s">
         <v>709</v>
       </c>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" hidden="1">
       <c r="A368" s="1" t="s">
         <v>711</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" hidden="1">
       <c r="A369" s="1" t="s">
         <v>713</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" hidden="1">
       <c r="A370" s="1" t="s">
         <v>715</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" hidden="1">
       <c r="A371" s="1" t="s">
         <v>718</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" hidden="1">
       <c r="A372" s="1" t="s">
         <v>721</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" hidden="1">
       <c r="A373" s="1" t="s">
         <v>724</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" hidden="1">
       <c r="A374" s="1" t="s">
         <v>727</v>
       </c>
@@ -11482,7 +11482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" hidden="1">
       <c r="A375" s="1" t="s">
         <v>730</v>
       </c>
@@ -11502,7 +11502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" hidden="1">
       <c r="A376" s="1" t="s">
         <v>733</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" hidden="1">
       <c r="A377" s="1" t="s">
         <v>736</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" hidden="1">
       <c r="A378" s="1" t="s">
         <v>739</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" hidden="1">
       <c r="A379" s="1" t="s">
         <v>742</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" hidden="1">
       <c r="A380" s="1" t="s">
         <v>745</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" hidden="1">
       <c r="A381" s="1" t="s">
         <v>748</v>
       </c>
@@ -11622,7 +11622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" hidden="1">
       <c r="A382" s="1" t="s">
         <v>750</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" hidden="1">
       <c r="A383" s="1" t="s">
         <v>753</v>
       </c>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" hidden="1">
       <c r="A384" s="1" t="s">
         <v>756</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" hidden="1">
       <c r="A385" s="1" t="s">
         <v>759</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" hidden="1">
       <c r="A386" s="1" t="s">
         <v>762</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" hidden="1">
       <c r="A387" s="1" t="s">
         <v>765</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" hidden="1">
       <c r="A388" s="1" t="s">
         <v>768</v>
       </c>
@@ -11762,7 +11762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" hidden="1">
       <c r="A389" s="1" t="s">
         <v>770</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" hidden="1">
       <c r="A390" s="1" t="s">
         <v>773</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" hidden="1">
       <c r="A391" s="1" t="s">
         <v>776</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" hidden="1">
       <c r="A392" s="1" t="s">
         <v>779</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" hidden="1">
       <c r="A393" s="1" t="s">
         <v>782</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" hidden="1">
       <c r="A394" s="1" t="s">
         <v>785</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" hidden="1">
       <c r="A395" s="1" t="s">
         <v>787</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" hidden="1">
       <c r="A396" s="1" t="s">
         <v>789</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" hidden="1">
       <c r="A397" s="1" t="s">
         <v>791</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" hidden="1">
       <c r="A398" s="1" t="s">
         <v>793</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" hidden="1">
       <c r="A399" s="1" t="s">
         <v>795</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" hidden="1">
       <c r="A400" s="1" t="s">
         <v>797</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" hidden="1">
       <c r="A401" s="1" t="s">
         <v>799</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" hidden="1">
       <c r="A402" s="1" t="s">
         <v>801</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" hidden="1">
       <c r="A403" s="1" t="s">
         <v>803</v>
       </c>
@@ -12062,7 +12062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" hidden="1">
       <c r="A404" s="1" t="s">
         <v>805</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" hidden="1">
       <c r="A405" s="1" t="s">
         <v>807</v>
       </c>
@@ -12102,7 +12102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" hidden="1">
       <c r="A406" s="1" t="s">
         <v>809</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" hidden="1">
       <c r="A407" s="1" t="s">
         <v>811</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" hidden="1">
       <c r="A408" s="1" t="s">
         <v>813</v>
       </c>
@@ -12162,7 +12162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" hidden="1">
       <c r="A409" s="1" t="s">
         <v>815</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" hidden="1">
       <c r="A410" s="1" t="s">
         <v>817</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" hidden="1">
       <c r="A411" s="1" t="s">
         <v>818</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" hidden="1">
       <c r="A412" s="1" t="s">
         <v>819</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" hidden="1">
       <c r="A413" s="1" t="s">
         <v>820</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" hidden="1">
       <c r="A414" s="1" t="s">
         <v>821</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" hidden="1">
       <c r="A415" s="1" t="s">
         <v>823</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" hidden="1">
       <c r="A416" s="1" t="s">
         <v>825</v>
       </c>
@@ -12322,7 +12322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" hidden="1">
       <c r="A417" s="1" t="s">
         <v>827</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" hidden="1">
       <c r="A418" s="1" t="s">
         <v>830</v>
       </c>
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" hidden="1">
       <c r="A419" s="1" t="s">
         <v>832</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" hidden="1">
       <c r="A420" s="1" t="s">
         <v>835</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" hidden="1">
       <c r="A421" s="1" t="s">
         <v>838</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" hidden="1">
       <c r="A422" s="1" t="s">
         <v>841</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" hidden="1">
       <c r="A423" s="1" t="s">
         <v>844</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" hidden="1">
       <c r="A424" s="1" t="s">
         <v>847</v>
       </c>
@@ -12482,7 +12482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" hidden="1">
       <c r="A425" s="1" t="s">
         <v>850</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" hidden="1">
       <c r="A426" s="1" t="s">
         <v>853</v>
       </c>
@@ -12522,7 +12522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" hidden="1">
       <c r="A427" s="1" t="s">
         <v>856</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" hidden="1">
       <c r="A428" s="1" t="s">
         <v>859</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" hidden="1">
       <c r="A429" s="1" t="s">
         <v>861</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" hidden="1">
       <c r="A430" s="1" t="s">
         <v>864</v>
       </c>
@@ -12602,7 +12602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" hidden="1">
       <c r="A431" s="1" t="s">
         <v>867</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" hidden="1">
       <c r="A432" s="1" t="s">
         <v>870</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" hidden="1">
       <c r="A433" s="1" t="s">
         <v>873</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" hidden="1">
       <c r="A434" s="1" t="s">
         <v>876</v>
       </c>
@@ -12682,7 +12682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" hidden="1">
       <c r="A435" s="1" t="s">
         <v>878</v>
       </c>
@@ -12702,7 +12702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" hidden="1">
       <c r="A436" s="1" t="s">
         <v>881</v>
       </c>
@@ -12722,7 +12722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" hidden="1">
       <c r="A437" s="1" t="s">
         <v>883</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" hidden="1">
       <c r="A438" s="1" t="s">
         <v>886</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" hidden="1">
       <c r="A439" s="1" t="s">
         <v>889</v>
       </c>
@@ -12782,7 +12782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" hidden="1">
       <c r="A440" s="1" t="s">
         <v>891</v>
       </c>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" hidden="1">
       <c r="A441" s="1" t="s">
         <v>894</v>
       </c>
@@ -12822,7 +12822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" hidden="1">
       <c r="A442" s="1" t="s">
         <v>897</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" hidden="1">
       <c r="A443" s="1" t="s">
         <v>900</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" hidden="1">
       <c r="A444" s="1" t="s">
         <v>903</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" hidden="1">
       <c r="A445" s="1" t="s">
         <v>906</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" hidden="1">
       <c r="A446" s="1" t="s">
         <v>909</v>
       </c>
@@ -12922,7 +12922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" hidden="1">
       <c r="A447" s="1" t="s">
         <v>912</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" hidden="1">
       <c r="A448" s="1" t="s">
         <v>915</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" hidden="1">
       <c r="A449" s="1" t="s">
         <v>918</v>
       </c>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" hidden="1">
       <c r="A450" s="1" t="s">
         <v>921</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" hidden="1">
       <c r="A451" s="1" t="s">
         <v>923</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" hidden="1">
       <c r="A452" s="1" t="s">
         <v>925</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" hidden="1">
       <c r="A453" s="1" t="s">
         <v>928</v>
       </c>
@@ -13062,7 +13062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" hidden="1">
       <c r="A454" s="1" t="s">
         <v>931</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" hidden="1">
       <c r="A455" s="1" t="s">
         <v>933</v>
       </c>
@@ -13102,7 +13102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" hidden="1">
       <c r="A456" s="1" t="s">
         <v>936</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" hidden="1">
       <c r="A457" s="1" t="s">
         <v>939</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" hidden="1">
       <c r="A458" s="1" t="s">
         <v>942</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" hidden="1">
       <c r="A459" s="1" t="s">
         <v>945</v>
       </c>
@@ -13182,7 +13182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" hidden="1">
       <c r="A460" s="1" t="s">
         <v>947</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" hidden="1">
       <c r="A461" s="1" t="s">
         <v>948</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" hidden="1">
       <c r="A462" s="1" t="s">
         <v>950</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" hidden="1">
       <c r="A463" s="1" t="s">
         <v>951</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" hidden="1">
       <c r="A464" s="1" t="s">
         <v>953</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" hidden="1">
       <c r="A465" s="1" t="s">
         <v>955</v>
       </c>
@@ -13302,7 +13302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" hidden="1">
       <c r="A466" s="1" t="s">
         <v>957</v>
       </c>
@@ -13322,7 +13322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" hidden="1">
       <c r="A467" s="1" t="s">
         <v>959</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" hidden="1">
       <c r="A468" s="1" t="s">
         <v>961</v>
       </c>
@@ -13362,7 +13362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" hidden="1">
       <c r="A469" s="1" t="s">
         <v>963</v>
       </c>
@@ -13382,7 +13382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" hidden="1">
       <c r="A470" s="1" t="s">
         <v>965</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" hidden="1">
       <c r="A471" s="1" t="s">
         <v>967</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" hidden="1">
       <c r="A472" s="1" t="s">
         <v>969</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" hidden="1">
       <c r="A473" s="1" t="s">
         <v>971</v>
       </c>
@@ -13462,7 +13462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" hidden="1">
       <c r="A474" s="1" t="s">
         <v>973</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" hidden="1">
       <c r="A475" s="1" t="s">
         <v>975</v>
       </c>
@@ -13502,7 +13502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" hidden="1">
       <c r="A476" s="1" t="s">
         <v>977</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" hidden="1">
       <c r="A477" s="1" t="s">
         <v>979</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" hidden="1">
       <c r="A478" s="1" t="s">
         <v>981</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" hidden="1">
       <c r="A479" s="1" t="s">
         <v>982</v>
       </c>
@@ -13582,7 +13582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" hidden="1">
       <c r="A480" s="1" t="s">
         <v>984</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" hidden="1">
       <c r="A481" s="1" t="s">
         <v>986</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" hidden="1">
       <c r="A482" s="1" t="s">
         <v>988</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" hidden="1">
       <c r="A483" s="1" t="s">
         <v>990</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" hidden="1">
       <c r="A484" s="1" t="s">
         <v>992</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" hidden="1">
       <c r="A485" s="1" t="s">
         <v>994</v>
       </c>
@@ -13702,7 +13702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" hidden="1">
       <c r="A486" s="1" t="s">
         <v>995</v>
       </c>
@@ -13722,7 +13722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" hidden="1">
       <c r="A487" s="1" t="s">
         <v>997</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" hidden="1">
       <c r="A488" s="1" t="s">
         <v>999</v>
       </c>
@@ -13762,7 +13762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" hidden="1">
       <c r="A489" s="1" t="s">
         <v>1001</v>
       </c>
@@ -13782,7 +13782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" hidden="1">
       <c r="A490" s="1" t="s">
         <v>1004</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" hidden="1">
       <c r="A491" s="1" t="s">
         <v>1006</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" hidden="1">
       <c r="A492" s="1" t="s">
         <v>1008</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" hidden="1">
       <c r="A493" s="1" t="s">
         <v>1010</v>
       </c>
@@ -13862,7 +13862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" hidden="1">
       <c r="A494" s="1" t="s">
         <v>1012</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" hidden="1">
       <c r="A495" s="1" t="s">
         <v>1015</v>
       </c>
@@ -13902,7 +13902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" hidden="1">
       <c r="A496" s="1" t="s">
         <v>1017</v>
       </c>
@@ -13922,7 +13922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" hidden="1">
       <c r="A497" s="1" t="s">
         <v>1019</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" hidden="1">
       <c r="A498" s="1" t="s">
         <v>1022</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" hidden="1">
       <c r="A499" s="1" t="s">
         <v>1024</v>
       </c>
@@ -13982,7 +13982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" hidden="1">
       <c r="A500" s="1" t="s">
         <v>1027</v>
       </c>
@@ -14002,7 +14002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" hidden="1">
       <c r="A501" s="1" t="s">
         <v>1029</v>
       </c>
@@ -14022,7 +14022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" hidden="1">
       <c r="A502" s="1" t="s">
         <v>1032</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" hidden="1">
       <c r="A503" s="1" t="s">
         <v>1034</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" hidden="1">
       <c r="A504" s="1" t="s">
         <v>1037</v>
       </c>
@@ -14082,7 +14082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" hidden="1">
       <c r="A505" s="1" t="s">
         <v>1040</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" hidden="1">
       <c r="A506" s="1" t="s">
         <v>1043</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" hidden="1">
       <c r="A507" s="1" t="s">
         <v>1045</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508">
+    <row r="508" hidden="1">
       <c r="A508" s="1" t="s">
         <v>1048</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" hidden="1">
       <c r="A509" s="1" t="s">
         <v>1051</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510">
+    <row r="510" hidden="1">
       <c r="A510" s="1" t="s">
         <v>1054</v>
       </c>
@@ -14202,7 +14202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" hidden="1">
       <c r="A511" s="1" t="s">
         <v>1057</v>
       </c>
@@ -14222,7 +14222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512">
+    <row r="512" hidden="1">
       <c r="A512" s="1" t="s">
         <v>1060</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" hidden="1">
       <c r="A513" s="1" t="s">
         <v>1063</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514">
+    <row r="514" hidden="1">
       <c r="A514" s="1" t="s">
         <v>1066</v>
       </c>
@@ -14282,7 +14282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" hidden="1">
       <c r="A515" s="1" t="s">
         <v>1069</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516">
+    <row r="516" hidden="1">
       <c r="A516" s="1" t="s">
         <v>1055</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" hidden="1">
       <c r="A517" s="1" t="s">
         <v>1072</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" hidden="1">
       <c r="A518" s="1" t="s">
         <v>1075</v>
       </c>
@@ -14362,7 +14362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" hidden="1">
       <c r="A519" s="1" t="s">
         <v>1078</v>
       </c>
@@ -14382,7 +14382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" hidden="1">
       <c r="A520" s="1" t="s">
         <v>1081</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521">
+    <row r="521" hidden="1">
       <c r="A521" s="1" t="s">
         <v>1084</v>
       </c>
@@ -14422,7 +14422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522">
+    <row r="522" hidden="1">
       <c r="A522" s="1" t="s">
         <v>1087</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523">
+    <row r="523" hidden="1">
       <c r="A523" s="1" t="s">
         <v>1090</v>
       </c>
@@ -14462,7 +14462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524">
+    <row r="524" hidden="1">
       <c r="A524" s="1" t="s">
         <v>1093</v>
       </c>
@@ -14482,7 +14482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" hidden="1">
       <c r="A525" s="1" t="s">
         <v>1096</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526">
+    <row r="526" hidden="1">
       <c r="A526" s="1" t="s">
         <v>1099</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527">
+    <row r="527" hidden="1">
       <c r="A527" s="1" t="s">
         <v>1102</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528">
+    <row r="528" hidden="1">
       <c r="A528" s="1" t="s">
         <v>1105</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529">
+    <row r="529" hidden="1">
       <c r="A529" s="1" t="s">
         <v>1108</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" hidden="1">
       <c r="A530" s="1" t="s">
         <v>1111</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531">
+    <row r="531" hidden="1">
       <c r="A531" s="1" t="s">
         <v>1114</v>
       </c>
@@ -14622,7 +14622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532">
+    <row r="532" hidden="1">
       <c r="A532" s="1" t="s">
         <v>1117</v>
       </c>
@@ -14642,7 +14642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533">
+    <row r="533" hidden="1">
       <c r="A533" s="1" t="s">
         <v>1119</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534">
+    <row r="534" hidden="1">
       <c r="A534" s="1" t="s">
         <v>1121</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" hidden="1">
       <c r="A535" s="1" t="s">
         <v>1123</v>
       </c>
@@ -14702,7 +14702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" hidden="1">
       <c r="A536" s="1" t="s">
         <v>1125</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" hidden="1">
       <c r="A537" s="1" t="s">
         <v>1127</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538">
+    <row r="538" hidden="1">
       <c r="A538" s="1" t="s">
         <v>1129</v>
       </c>
@@ -14762,7 +14762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539">
+    <row r="539" hidden="1">
       <c r="A539" s="1" t="s">
         <v>1131</v>
       </c>
@@ -14782,7 +14782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540">
+    <row r="540" hidden="1">
       <c r="A540" s="1" t="s">
         <v>1134</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541">
+    <row r="541" hidden="1">
       <c r="A541" s="1" t="s">
         <v>1137</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542">
+    <row r="542" hidden="1">
       <c r="A542" s="1" t="s">
         <v>1140</v>
       </c>
@@ -14842,7 +14842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" hidden="1">
       <c r="A543" s="1" t="s">
         <v>1143</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" hidden="1">
       <c r="A544" s="1" t="s">
         <v>1145</v>
       </c>
@@ -14882,7 +14882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545">
+    <row r="545" hidden="1">
       <c r="A545" s="1" t="s">
         <v>1147</v>
       </c>
@@ -14902,7 +14902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" hidden="1">
       <c r="A546" s="1" t="s">
         <v>1149</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" hidden="1">
       <c r="A547" s="1" t="s">
         <v>1152</v>
       </c>
@@ -14942,7 +14942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" hidden="1">
       <c r="A548" s="1" t="s">
         <v>1155</v>
       </c>
@@ -14962,7 +14962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" hidden="1">
       <c r="A549" s="1" t="s">
         <v>1158</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550">
+    <row r="550" hidden="1">
       <c r="A550" s="1" t="s">
         <v>1161</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551">
+    <row r="551" hidden="1">
       <c r="A551" s="1" t="s">
         <v>1164</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552">
+    <row r="552" hidden="1">
       <c r="A552" s="1" t="s">
         <v>1167</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553">
+    <row r="553" hidden="1">
       <c r="A553" s="1" t="s">
         <v>1170</v>
       </c>
@@ -15062,7 +15062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554">
+    <row r="554" hidden="1">
       <c r="A554" s="1" t="s">
         <v>1173</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555">
+    <row r="555" hidden="1">
       <c r="A555" s="1" t="s">
         <v>1176</v>
       </c>
@@ -15102,7 +15102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556">
+    <row r="556" hidden="1">
       <c r="A556" s="1" t="s">
         <v>1179</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557">
+    <row r="557" hidden="1">
       <c r="A557" s="1" t="s">
         <v>1182</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558">
+    <row r="558" hidden="1">
       <c r="A558" s="1" t="s">
         <v>1185</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559">
+    <row r="559" hidden="1">
       <c r="A559" s="1" t="s">
         <v>1188</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560">
+    <row r="560" hidden="1">
       <c r="A560" s="1" t="s">
         <v>1189</v>
       </c>
@@ -15202,7 +15202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561">
+    <row r="561" hidden="1">
       <c r="A561" s="1" t="s">
         <v>1192</v>
       </c>
@@ -15222,7 +15222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" hidden="1">
       <c r="A562" s="1" t="s">
         <v>1194</v>
       </c>
@@ -15242,7 +15242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" hidden="1">
       <c r="A563" s="1" t="s">
         <v>1196</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564">
+    <row r="564" hidden="1">
       <c r="A564" s="1" t="s">
         <v>1198</v>
       </c>
@@ -15282,7 +15282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565">
+    <row r="565" hidden="1">
       <c r="A565" s="1" t="s">
         <v>1200</v>
       </c>
@@ -15302,7 +15302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566">
+    <row r="566" hidden="1">
       <c r="A566" s="1" t="s">
         <v>1202</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567">
+    <row r="567" hidden="1">
       <c r="A567" s="1" t="s">
         <v>1204</v>
       </c>
@@ -15342,7 +15342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568">
+    <row r="568" hidden="1">
       <c r="A568" s="1" t="s">
         <v>1206</v>
       </c>
@@ -15362,7 +15362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569">
+    <row r="569" hidden="1">
       <c r="A569" s="1" t="s">
         <v>1208</v>
       </c>
@@ -15382,7 +15382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570">
+    <row r="570" hidden="1">
       <c r="A570" s="1" t="s">
         <v>1210</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571">
+    <row r="571" hidden="1">
       <c r="A571" s="1" t="s">
         <v>1212</v>
       </c>
@@ -15422,7 +15422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" hidden="1">
       <c r="A572" s="1" t="s">
         <v>1214</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573">
+    <row r="573" hidden="1">
       <c r="A573" s="1" t="s">
         <v>1216</v>
       </c>
@@ -15462,7 +15462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574">
+    <row r="574" hidden="1">
       <c r="A574" s="1" t="s">
         <v>1218</v>
       </c>
@@ -15482,7 +15482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575">
+    <row r="575" hidden="1">
       <c r="A575" s="1" t="s">
         <v>1220</v>
       </c>
@@ -15502,7 +15502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576">
+    <row r="576" hidden="1">
       <c r="A576" s="1" t="s">
         <v>1222</v>
       </c>
@@ -15522,7 +15522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577">
+    <row r="577" hidden="1">
       <c r="A577" s="1" t="s">
         <v>1224</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578">
+    <row r="578" hidden="1">
       <c r="A578" s="1" t="s">
         <v>1226</v>
       </c>
@@ -15562,7 +15562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579">
+    <row r="579" hidden="1">
       <c r="A579" s="1" t="s">
         <v>1228</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580">
+    <row r="580" hidden="1">
       <c r="A580" s="1" t="s">
         <v>1230</v>
       </c>
@@ -15602,7 +15602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581">
+    <row r="581" hidden="1">
       <c r="A581" s="1" t="s">
         <v>1232</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582">
+    <row r="582" hidden="1">
       <c r="A582" s="1" t="s">
         <v>1234</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583">
+    <row r="583" hidden="1">
       <c r="A583" s="1" t="s">
         <v>1236</v>
       </c>
@@ -15662,7 +15662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584">
+    <row r="584" hidden="1">
       <c r="A584" s="1" t="s">
         <v>1238</v>
       </c>
@@ -15682,7 +15682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585">
+    <row r="585" hidden="1">
       <c r="A585" s="1" t="s">
         <v>1240</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586">
+    <row r="586" hidden="1">
       <c r="A586" s="1" t="s">
         <v>1241</v>
       </c>
@@ -18635,7 +18635,18 @@
       <c r="E1002" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$F$586"/>
+  <autoFilter ref="$A$1:$F$586">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="F14"/>
+        <filter val="F13"/>
+        <filter val="F16"/>
+        <filter val="F15"/>
+        <filter val="F18"/>
+        <filter val="F17"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>